--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.24493193744794</v>
+        <v>6.864801439835291</v>
       </c>
       <c r="D2" t="n">
-        <v>43.44351679722374</v>
+        <v>7.059571479548858</v>
       </c>
       <c r="E2" t="n">
-        <v>12.15710646141195</v>
+        <v>1.975529799979441</v>
       </c>
       <c r="F2" t="n">
-        <v>12.61745958943557</v>
+        <v>2.050337183283281</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.49731067467766</v>
+        <v>4.630812984635119</v>
       </c>
       <c r="D3" t="n">
-        <v>28.08005904217843</v>
+        <v>4.563009594353995</v>
       </c>
       <c r="E3" t="n">
-        <v>12.15710646141195</v>
+        <v>1.975529799979441</v>
       </c>
       <c r="F3" t="n">
-        <v>12.61745958943557</v>
+        <v>2.050337183283281</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.18948303973607</v>
+        <v>3.605790993957111</v>
       </c>
       <c r="D4" t="n">
-        <v>21.2127810731361</v>
+        <v>3.447076924384616</v>
       </c>
       <c r="E4" t="n">
-        <v>12.15710646141195</v>
+        <v>1.975529799979441</v>
       </c>
       <c r="F4" t="n">
-        <v>12.61745958943557</v>
+        <v>2.050337183283281</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.29139900927134</v>
+        <v>4.597352339006593</v>
       </c>
       <c r="D5" t="n">
-        <v>31.53444321121539</v>
+        <v>5.124347021822501</v>
       </c>
       <c r="E5" t="n">
-        <v>12.15710646141195</v>
+        <v>1.975529799979441</v>
       </c>
       <c r="F5" t="n">
-        <v>12.61745958943557</v>
+        <v>2.050337183283281</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.98970042208336</v>
+        <v>3.085826318588547</v>
       </c>
       <c r="D6" t="n">
-        <v>20.33807129982218</v>
+        <v>3.304936586221104</v>
       </c>
       <c r="E6" t="n">
-        <v>12.15710646141195</v>
+        <v>1.975529799979441</v>
       </c>
       <c r="F6" t="n">
-        <v>12.61745958943557</v>
+        <v>2.050337183283281</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.05967201499587</v>
+        <v>4.88469670243683</v>
       </c>
       <c r="D7" t="n">
-        <v>31.3833459929714</v>
+        <v>5.099793723857853</v>
       </c>
       <c r="E7" t="n">
-        <v>12.15710646141195</v>
+        <v>1.975529799979441</v>
       </c>
       <c r="F7" t="n">
-        <v>12.61745958943557</v>
+        <v>2.050337183283281</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>2.141300257663598</v>
+        <v>0.3479612918703346</v>
       </c>
       <c r="D8" t="n">
-        <v>3.310205793525</v>
+        <v>0.5379084414478125</v>
       </c>
       <c r="E8" t="n">
-        <v>12.15710646141195</v>
+        <v>1.975529799979441</v>
       </c>
       <c r="F8" t="n">
-        <v>12.61745958943557</v>
+        <v>2.050337183283281</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>4.930846120438814</v>
+        <v>0.8012624945713074</v>
       </c>
       <c r="D9" t="n">
-        <v>3.887342632779289</v>
+        <v>0.6316931778266345</v>
       </c>
       <c r="E9" t="n">
-        <v>12.15710646141195</v>
+        <v>1.975529799979441</v>
       </c>
       <c r="F9" t="n">
-        <v>12.61745958943557</v>
+        <v>2.050337183283281</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.162742643238</v>
+        <v>4.576445679526176</v>
       </c>
       <c r="D10" t="n">
-        <v>27.81405662551808</v>
+        <v>4.519784201646689</v>
       </c>
       <c r="E10" t="n">
-        <v>12.15710646141195</v>
+        <v>1.975529799979441</v>
       </c>
       <c r="F10" t="n">
-        <v>12.61745958943557</v>
+        <v>2.050337183283281</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>8.122058162694104</v>
+        <v>1.319834451437792</v>
       </c>
       <c r="D11" t="n">
-        <v>7.792903451799843</v>
+        <v>1.266346810917474</v>
       </c>
       <c r="E11" t="n">
-        <v>12.15710646141195</v>
+        <v>1.975529799979441</v>
       </c>
       <c r="F11" t="n">
-        <v>12.61745958943557</v>
+        <v>2.050337183283281</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
